--- a/Excel/TextFunctions1.xlsx
+++ b/Excel/TextFunctions1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E1500B-EBF2-4B33-976F-EAAC771BAE25}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979ED8D-9C99-4125-9973-6FF545DAFBC4}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="1" xr2:uid="{F66161BB-47FA-4D86-A75E-82214A4B244F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="2" xr2:uid="{F66161BB-47FA-4D86-A75E-82214A4B244F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex1" sheetId="2" r:id="rId1"/>
     <sheet name="Ex2" sheetId="1" r:id="rId2"/>
+    <sheet name="Ex3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -185,6 +186,27 @@
   </si>
   <si>
     <t>LEN</t>
+  </si>
+  <si>
+    <t>SET India</t>
+  </si>
+  <si>
+    <t>Ashish Chanchlani Vines</t>
+  </si>
+  <si>
+    <t>Technical Guruji</t>
+  </si>
+  <si>
+    <t>Canal Kondzilla</t>
+  </si>
+  <si>
+    <t>UPPERCASE</t>
+  </si>
+  <si>
+    <t>lowercase</t>
+  </si>
+  <si>
+    <t>Proper Case</t>
   </si>
 </sst>
 </file>
@@ -301,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -333,9 +355,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -344,6 +363,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -811,12 +839,12 @@
         <f t="shared" si="3"/>
         <v>1.7241379310344827</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
@@ -1233,8 +1261,8 @@
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="19.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.90625" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -1273,15 +1301,15 @@
       <c r="D2" s="6">
         <v>250</v>
       </c>
-      <c r="E2" s="15" t="str">
-        <f>TRIM(B2)</f>
+      <c r="E2" s="14" t="str">
+        <f t="shared" ref="E2:E21" si="0">TRIM(B2)</f>
         <v>T-serIES</v>
       </c>
-      <c r="F2" s="14">
-        <f>LEN(B2)</f>
+      <c r="F2" s="13">
+        <f t="shared" ref="F2:F21" si="1">LEN(B2)</f>
         <v>8</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="16">
         <f>LEN(E2)</f>
         <v>8</v>
       </c>
@@ -1299,16 +1327,16 @@
       <c r="D3" s="6">
         <v>157</v>
       </c>
-      <c r="E3" s="16" t="str">
+      <c r="E3" s="15" t="str">
         <f>TRIM(B3)</f>
         <v>SET India</v>
       </c>
-      <c r="F3" s="14">
-        <f>LEN(B3)</f>
+      <c r="F3" s="13">
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="G3" s="17">
-        <f t="shared" ref="G3:G21" si="0">LEN(E3)</f>
+      <c r="G3" s="16">
+        <f t="shared" ref="G3:G21" si="2">LEN(E3)</f>
         <v>9</v>
       </c>
     </row>
@@ -1326,15 +1354,15 @@
         <v>94</v>
       </c>
       <c r="E4" s="8" t="str">
-        <f>TRIM(B4)</f>
+        <f t="shared" si="0"/>
         <v>Zee Music company</v>
       </c>
-      <c r="F4" s="14">
-        <f>LEN(B4)</f>
+      <c r="F4" s="13">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G4" s="17">
-        <f t="shared" si="0"/>
+      <c r="G4" s="16">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
@@ -1352,15 +1380,15 @@
         <v>52</v>
       </c>
       <c r="E5" s="8" t="str">
-        <f>TRIM(B5)</f>
+        <f t="shared" si="0"/>
         <v>Sony Music INDIA</v>
       </c>
-      <c r="F5" s="14">
-        <f>LEN(B5)</f>
+      <c r="F5" s="13">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G5" s="17">
-        <f t="shared" si="0"/>
+      <c r="G5" s="16">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -1378,15 +1406,15 @@
         <v>50</v>
       </c>
       <c r="E6" s="8" t="str">
-        <f>TRIM(B6)</f>
+        <f t="shared" si="0"/>
         <v>Aaj Tak</v>
       </c>
-      <c r="F6" s="14">
-        <f>LEN(B6)</f>
+      <c r="F6" s="13">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G6" s="17">
-        <f t="shared" si="0"/>
+      <c r="G6" s="16">
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1404,15 +1432,15 @@
         <v>45</v>
       </c>
       <c r="E7" s="8" t="str">
-        <f>TRIM(B7)</f>
+        <f t="shared" si="0"/>
         <v>YRF</v>
       </c>
-      <c r="F7" s="14">
-        <f>LEN(B7)</f>
+      <c r="F7" s="13">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G7" s="17">
-        <f t="shared" si="0"/>
+      <c r="G7" s="16">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -1429,16 +1457,16 @@
       <c r="D8" s="6">
         <v>40</v>
       </c>
-      <c r="E8" s="16" t="str">
-        <f>TRIM(B8)</f>
+      <c r="E8" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>CarryMINATI</v>
       </c>
-      <c r="F8" s="14">
-        <f>LEN(B8)</f>
+      <c r="F8" s="13">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G8" s="17">
-        <f t="shared" si="0"/>
+      <c r="G8" s="16">
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -1455,16 +1483,16 @@
       <c r="D9" s="6">
         <v>32</v>
       </c>
-      <c r="E9" s="16" t="str">
-        <f>TRIM(B9)</f>
+      <c r="E9" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>Ashish Chanchlani Vines</v>
       </c>
-      <c r="F9" s="14">
-        <f>LEN(B9)</f>
+      <c r="F9" s="13">
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="G9" s="17">
-        <f t="shared" si="0"/>
+      <c r="G9" s="16">
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
@@ -1482,15 +1510,15 @@
         <v>26</v>
       </c>
       <c r="E10" s="8" t="str">
-        <f>TRIM(B10)</f>
+        <f t="shared" si="0"/>
         <v>BB Ki Vines</v>
       </c>
-      <c r="F10" s="14">
-        <f>LEN(B10)</f>
+      <c r="F10" s="13">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G10" s="17">
-        <f t="shared" si="0"/>
+      <c r="G10" s="16">
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -1507,16 +1535,16 @@
       <c r="D11" s="6">
         <v>22</v>
       </c>
-      <c r="E11" s="16" t="str">
-        <f>TRIM(B11)</f>
+      <c r="E11" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>Technical Guruji</v>
       </c>
-      <c r="F11" s="14">
-        <f>LEN(B11)</f>
+      <c r="F11" s="13">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="G11" s="17">
-        <f t="shared" si="0"/>
+      <c r="G11" s="16">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -1534,15 +1562,15 @@
         <v>176</v>
       </c>
       <c r="E12" s="8" t="str">
-        <f>TRIM(B12)</f>
+        <f t="shared" si="0"/>
         <v>MrBeast</v>
       </c>
-      <c r="F12" s="14">
-        <f>LEN(B12)</f>
+      <c r="F12" s="13">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G12" s="17">
-        <f t="shared" si="0"/>
+      <c r="G12" s="16">
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1559,16 +1587,16 @@
       <c r="D13" s="6">
         <v>111</v>
       </c>
-      <c r="E13" s="16" t="str">
-        <f>TRIM(B13)</f>
+      <c r="E13" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>PEwdiePie</v>
       </c>
-      <c r="F13" s="14">
-        <f>LEN(B13)</f>
+      <c r="F13" s="13">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G13" s="17">
-        <f t="shared" si="0"/>
+      <c r="G13" s="16">
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -1585,16 +1613,16 @@
       <c r="D14" s="6">
         <v>78</v>
       </c>
-      <c r="E14" s="16" t="str">
-        <f>TRIM(B14)</f>
+      <c r="E14" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>5-minute CRAFTS</v>
       </c>
-      <c r="F14" s="14">
-        <f>LEN(B14)</f>
+      <c r="F14" s="13">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G14" s="17">
-        <f t="shared" si="0"/>
+      <c r="G14" s="16">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1612,15 +1640,15 @@
         <v>106</v>
       </c>
       <c r="E15" s="8" t="str">
-        <f>TRIM(B15)</f>
+        <f t="shared" si="0"/>
         <v>likeNastia</v>
       </c>
-      <c r="F15" s="14">
-        <f>LEN(B15)</f>
+      <c r="F15" s="13">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G15" s="17">
-        <f t="shared" si="0"/>
+      <c r="G15" s="16">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -1638,15 +1666,15 @@
         <v>163</v>
       </c>
       <c r="E16" s="8" t="str">
-        <f>TRIM(B16)</f>
+        <f t="shared" si="0"/>
         <v>coComelon - Nursery rhymes</v>
       </c>
-      <c r="F16" s="14">
-        <f>LEN(B16)</f>
+      <c r="F16" s="13">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="G16" s="17">
-        <f t="shared" si="0"/>
+      <c r="G16" s="16">
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
     </row>
@@ -1663,16 +1691,16 @@
       <c r="D17" s="6">
         <v>66</v>
       </c>
-      <c r="E17" s="16" t="str">
-        <f>TRIM(B17)</f>
+      <c r="E17" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>Canal Kondzilla</v>
       </c>
-      <c r="F17" s="14">
-        <f>LEN(B17)</f>
+      <c r="F17" s="13">
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="G17" s="17">
-        <f t="shared" si="0"/>
+      <c r="G17" s="16">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1690,15 +1718,15 @@
         <v>115</v>
       </c>
       <c r="E18" s="8" t="str">
-        <f>TRIM(B18)</f>
+        <f t="shared" si="0"/>
         <v>kids D Iana Show</v>
       </c>
-      <c r="F18" s="14">
-        <f>LEN(B18)</f>
+      <c r="F18" s="13">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G18" s="17">
-        <f t="shared" si="0"/>
+      <c r="G18" s="16">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -1716,15 +1744,15 @@
         <v>44</v>
       </c>
       <c r="E19" s="8" t="str">
-        <f>TRIM(B19)</f>
+        <f t="shared" si="0"/>
         <v>Badabun</v>
       </c>
-      <c r="F19" s="14">
-        <f>LEN(B19)</f>
+      <c r="F19" s="13">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G19" s="17">
-        <f t="shared" si="0"/>
+      <c r="G19" s="16">
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1742,15 +1770,15 @@
         <v>25</v>
       </c>
       <c r="E20" s="8" t="str">
-        <f>TRIM(B20)</f>
+        <f t="shared" si="0"/>
         <v>VanossGaming</v>
       </c>
-      <c r="F20" s="14">
-        <f>LEN(B20)</f>
+      <c r="F20" s="13">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G20" s="17">
-        <f t="shared" si="0"/>
+      <c r="G20" s="16">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
@@ -1768,17 +1796,620 @@
         <v>35</v>
       </c>
       <c r="E21" s="8" t="str">
-        <f>TRIM(B21)</f>
+        <f t="shared" si="0"/>
         <v>Markiplier</v>
       </c>
-      <c r="F21" s="14">
-        <f>LEN(B21)</f>
+      <c r="F21" s="13">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G21" s="17">
-        <f t="shared" si="0"/>
+      <c r="G21" s="16">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB61644-DB3C-4B35-9C75-4CC5D0DA42B6}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" customWidth="1"/>
+    <col min="4" max="4" width="21.90625" customWidth="1"/>
+    <col min="5" max="5" width="30.90625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6">
+        <v>250</v>
+      </c>
+      <c r="E2" s="19" t="str">
+        <f>UPPER(B2)</f>
+        <v>T-SERIES</v>
+      </c>
+      <c r="F2" s="8" t="str">
+        <f>UPPER(1784345453)</f>
+        <v>1784345453</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f>LOWER(B2)</f>
+        <v>t-series</v>
+      </c>
+      <c r="H2" s="8" t="str">
+        <f>PROPER(B2)</f>
+        <v>T-Series</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6">
+        <v>157</v>
+      </c>
+      <c r="E3" s="19" t="str">
+        <f t="shared" ref="E3:E21" si="0">UPPER(B3)</f>
+        <v>SET INDIA</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="str">
+        <f t="shared" ref="G3:G21" si="1">LOWER(B3)</f>
+        <v>set india</v>
+      </c>
+      <c r="H3" s="8" t="str">
+        <f t="shared" ref="H3:H21" si="2">PROPER(B3)</f>
+        <v>Set India</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6">
+        <v>94</v>
+      </c>
+      <c r="E4" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>ZEE MUSIC COMPANY</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>zee music company</v>
+      </c>
+      <c r="H4" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Zee Music Company</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6">
+        <v>52</v>
+      </c>
+      <c r="E5" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>SONY MUSIC INDIA</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>sony music india</v>
+      </c>
+      <c r="H5" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Sony Music India</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6">
+        <v>50</v>
+      </c>
+      <c r="E6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>AAJ TAK</v>
+      </c>
+      <c r="F6" s="8" t="str">
+        <f>UPPER("@#$")</f>
+        <v>@#$</v>
+      </c>
+      <c r="G6" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>aaj tak</v>
+      </c>
+      <c r="H6" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Aaj Tak</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="6">
+        <v>45</v>
+      </c>
+      <c r="E7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>YRF</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>yrf</v>
+      </c>
+      <c r="H7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Yrf</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6">
+        <v>40</v>
+      </c>
+      <c r="E8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>CARRYMINATI</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>carryminati</v>
+      </c>
+      <c r="H8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Carryminati</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6">
+        <v>32</v>
+      </c>
+      <c r="E9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>ASHISH CHANCHLANI VINES</v>
+      </c>
+      <c r="F9" s="8" t="str">
+        <f>UPPER("Chintu123")</f>
+        <v>CHINTU123</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>ashish chanchlani vines</v>
+      </c>
+      <c r="H9" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Ashish Chanchlani Vines</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="6">
+        <v>26</v>
+      </c>
+      <c r="E10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>BB KI VINES</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>bb ki vines</v>
+      </c>
+      <c r="H10" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Bb Ki Vines</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6">
+        <v>22</v>
+      </c>
+      <c r="E11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>TECHNICAL GURUJI</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>technical guruji</v>
+      </c>
+      <c r="H11" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Technical Guruji</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="6">
+        <v>176</v>
+      </c>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>MRBEAST</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>mrbeast</v>
+      </c>
+      <c r="H12" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Mrbeast</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6">
+        <v>111</v>
+      </c>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>PEWDIEPIE</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>pewdiepie</v>
+      </c>
+      <c r="H13" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Pewdiepie</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="6">
+        <v>78</v>
+      </c>
+      <c r="E14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>5-MINUTE CRAFTS</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>5-minute crafts</v>
+      </c>
+      <c r="H14" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>5-Minute Crafts</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="6">
+        <v>106</v>
+      </c>
+      <c r="E15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>LIKENASTIA</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>likenastia</v>
+      </c>
+      <c r="H15" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Likenastia</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6">
+        <v>163</v>
+      </c>
+      <c r="E16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>COCOMELON - NURSERY RHYMES</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>cocomelon - nursery rhymes</v>
+      </c>
+      <c r="H16" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Cocomelon - Nursery Rhymes</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="6">
+        <v>66</v>
+      </c>
+      <c r="E17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>CANAL KONDZILLA</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>canal kondzilla</v>
+      </c>
+      <c r="H17" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Canal Kondzilla</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="6">
+        <v>115</v>
+      </c>
+      <c r="E18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>KIDS D IANA SHOW</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>kids d iana show</v>
+      </c>
+      <c r="H18" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Kids D Iana Show</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="6">
+        <v>44</v>
+      </c>
+      <c r="E19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>BADABUN</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>badabun</v>
+      </c>
+      <c r="H19" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Badabun</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="6">
+        <v>25</v>
+      </c>
+      <c r="E20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>VANOSSGAMING</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>vanossgaming</v>
+      </c>
+      <c r="H20" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Vanossgaming</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="6">
+        <v>35</v>
+      </c>
+      <c r="E21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>MARKIPLIER</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>markiplier</v>
+      </c>
+      <c r="H21" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Markiplier</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E22" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/TextFunctions1.xlsx
+++ b/Excel/TextFunctions1.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979ED8D-9C99-4125-9973-6FF545DAFBC4}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08C6A78-891A-47F1-8F15-D1D5388DF6E5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="2" xr2:uid="{F66161BB-47FA-4D86-A75E-82214A4B244F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="4" xr2:uid="{F66161BB-47FA-4D86-A75E-82214A4B244F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex1" sheetId="2" r:id="rId1"/>
     <sheet name="Ex2" sheetId="1" r:id="rId2"/>
     <sheet name="Ex3" sheetId="3" r:id="rId3"/>
+    <sheet name="Ex4" sheetId="4" r:id="rId4"/>
+    <sheet name="Ex5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -207,13 +209,46 @@
   </si>
   <si>
     <t>Proper Case</t>
+  </si>
+  <si>
+    <t>FullName</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Requirment</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Pavan Kumar</t>
+  </si>
+  <si>
+    <t>Zameeruddin Syed</t>
+  </si>
+  <si>
+    <t>Shiva Kumar</t>
+  </si>
+  <si>
+    <t>Sai Chiru</t>
+  </si>
+  <si>
+    <t>FIND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +276,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -287,7 +330,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -319,11 +362,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -372,6 +424,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2415,4 +2487,243 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8071F947-6791-4CC0-88D3-DDF733EEBF95}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.36328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="17.08984375" style="25" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="25" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="E1" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="27"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="6">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="27" t="str">
+        <f>LEFT(A2,5)</f>
+        <v>Pavan</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <f>LEFT(A3,11)</f>
+        <v>Zameeruddin</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <f>LEFT(A4,5)</f>
+        <v>Shiva</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <f>LEFT(A5,3)</f>
+        <v>Sai</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="6">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="27" t="str">
+        <f>RIGHT(A2,5)</f>
+        <v>Kumar</v>
+      </c>
+      <c r="G3" s="27" t="str">
+        <f>RIGHT(A3,4)</f>
+        <v>Syed</v>
+      </c>
+      <c r="H3" s="27" t="str">
+        <f>RIGHT(A4,5)</f>
+        <v>Kumar</v>
+      </c>
+      <c r="I3" s="27" t="str">
+        <f>RIGHT(A5,5)</f>
+        <v>Chiru</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="6">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="6">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6">
+        <v>200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CDF229-8701-4776-BEC2-C869777DA5B4}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" style="10"/>
+    <col min="7" max="7" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="6">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="E2" s="10">
+        <f>FIND(" ",A2)</f>
+        <v>6</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f>LEFT(A2,E2)</f>
+        <v xml:space="preserve">Pavan </v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="6">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="E3" s="10">
+        <f t="shared" ref="E3:E5" si="0">FIND(" ",A3)</f>
+        <v>12</v>
+      </c>
+      <c r="G3" s="8" t="str">
+        <f t="shared" ref="G3:G5" si="1">LEFT(A3,E3)</f>
+        <v xml:space="preserve">Zameeruddin </v>
+      </c>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="6">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6">
+        <v>200000</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Shiva </v>
+      </c>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="6">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6">
+        <v>200000</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Sai </v>
+      </c>
+      <c r="H5" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Excel/TextFunctions1.xlsx
+++ b/Excel/TextFunctions1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08C6A78-891A-47F1-8F15-D1D5388DF6E5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AE885B-EEF5-43ED-8CC5-93601C70233A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="4" xr2:uid="{F66161BB-47FA-4D86-A75E-82214A4B244F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="7" xr2:uid="{F66161BB-47FA-4D86-A75E-82214A4B244F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex1" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Ex3" sheetId="3" r:id="rId3"/>
     <sheet name="Ex4" sheetId="4" r:id="rId4"/>
     <sheet name="Ex5" sheetId="5" r:id="rId5"/>
+    <sheet name="Ex6" sheetId="6" r:id="rId6"/>
+    <sheet name="Ex7" sheetId="7" r:id="rId7"/>
+    <sheet name="Ex8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -242,6 +245,51 @@
   </si>
   <si>
     <t>FIND</t>
+  </si>
+  <si>
+    <t>Len</t>
+  </si>
+  <si>
+    <t>LastNameCharactersCount</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Pavan</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>Zameeruddin</t>
+  </si>
+  <si>
+    <t>Syed</t>
+  </si>
+  <si>
+    <t>Shiva</t>
+  </si>
+  <si>
+    <t>Sai</t>
+  </si>
+  <si>
+    <t>Chiru</t>
+  </si>
+  <si>
+    <t>FullNameWithMobile</t>
+  </si>
+  <si>
+    <t>simpleMail</t>
+  </si>
+  <si>
+    <t>Maillast4digits</t>
+  </si>
+  <si>
+    <t>mailfirst4digits</t>
+  </si>
+  <si>
+    <t>Mailmid4digits</t>
   </si>
 </sst>
 </file>
@@ -330,7 +378,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -371,11 +419,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -415,9 +474,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -443,6 +499,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -911,12 +979,12 @@
         <f t="shared" si="3"/>
         <v>1.7241379310344827</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
@@ -1895,7 +1963,7 @@
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="25.26953125" customWidth="1"/>
     <col min="4" max="4" width="21.90625" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="30.90625" style="20" customWidth="1"/>
     <col min="6" max="6" width="19.453125" customWidth="1"/>
     <col min="7" max="7" width="24.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.6328125" bestFit="1" customWidth="1"/>
@@ -1914,16 +1982,16 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1940,7 +2008,7 @@
       <c r="D2" s="6">
         <v>250</v>
       </c>
-      <c r="E2" s="19" t="str">
+      <c r="E2" s="18" t="str">
         <f>UPPER(B2)</f>
         <v>T-SERIES</v>
       </c>
@@ -1970,7 +2038,7 @@
       <c r="D3" s="6">
         <v>157</v>
       </c>
-      <c r="E3" s="19" t="str">
+      <c r="E3" s="18" t="str">
         <f t="shared" ref="E3:E21" si="0">UPPER(B3)</f>
         <v>SET INDIA</v>
       </c>
@@ -1997,7 +2065,7 @@
       <c r="D4" s="6">
         <v>94</v>
       </c>
-      <c r="E4" s="19" t="str">
+      <c r="E4" s="18" t="str">
         <f t="shared" si="0"/>
         <v>ZEE MUSIC COMPANY</v>
       </c>
@@ -2024,11 +2092,11 @@
       <c r="D5" s="6">
         <v>52</v>
       </c>
-      <c r="E5" s="19" t="str">
+      <c r="E5" s="18" t="str">
         <f t="shared" si="0"/>
         <v>SONY MUSIC INDIA</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>57</v>
       </c>
       <c r="G5" s="8" t="str">
@@ -2053,7 +2121,7 @@
       <c r="D6" s="6">
         <v>50</v>
       </c>
-      <c r="E6" s="19" t="str">
+      <c r="E6" s="18" t="str">
         <f t="shared" si="0"/>
         <v>AAJ TAK</v>
       </c>
@@ -2083,7 +2151,7 @@
       <c r="D7" s="6">
         <v>45</v>
       </c>
-      <c r="E7" s="19" t="str">
+      <c r="E7" s="18" t="str">
         <f t="shared" si="0"/>
         <v>YRF</v>
       </c>
@@ -2110,11 +2178,11 @@
       <c r="D8" s="6">
         <v>40</v>
       </c>
-      <c r="E8" s="19" t="str">
+      <c r="E8" s="18" t="str">
         <f t="shared" si="0"/>
         <v>CARRYMINATI</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>57</v>
       </c>
       <c r="G8" s="8" t="str">
@@ -2139,7 +2207,7 @@
       <c r="D9" s="6">
         <v>32</v>
       </c>
-      <c r="E9" s="19" t="str">
+      <c r="E9" s="18" t="str">
         <f t="shared" si="0"/>
         <v>ASHISH CHANCHLANI VINES</v>
       </c>
@@ -2169,7 +2237,7 @@
       <c r="D10" s="6">
         <v>26</v>
       </c>
-      <c r="E10" s="19" t="str">
+      <c r="E10" s="18" t="str">
         <f t="shared" si="0"/>
         <v>BB KI VINES</v>
       </c>
@@ -2196,7 +2264,7 @@
       <c r="D11" s="6">
         <v>22</v>
       </c>
-      <c r="E11" s="19" t="str">
+      <c r="E11" s="18" t="str">
         <f t="shared" si="0"/>
         <v>TECHNICAL GURUJI</v>
       </c>
@@ -2223,7 +2291,7 @@
       <c r="D12" s="6">
         <v>176</v>
       </c>
-      <c r="E12" s="19" t="str">
+      <c r="E12" s="18" t="str">
         <f t="shared" si="0"/>
         <v>MRBEAST</v>
       </c>
@@ -2250,7 +2318,7 @@
       <c r="D13" s="6">
         <v>111</v>
       </c>
-      <c r="E13" s="19" t="str">
+      <c r="E13" s="18" t="str">
         <f t="shared" si="0"/>
         <v>PEWDIEPIE</v>
       </c>
@@ -2277,7 +2345,7 @@
       <c r="D14" s="6">
         <v>78</v>
       </c>
-      <c r="E14" s="19" t="str">
+      <c r="E14" s="18" t="str">
         <f t="shared" si="0"/>
         <v>5-MINUTE CRAFTS</v>
       </c>
@@ -2304,7 +2372,7 @@
       <c r="D15" s="6">
         <v>106</v>
       </c>
-      <c r="E15" s="19" t="str">
+      <c r="E15" s="18" t="str">
         <f t="shared" si="0"/>
         <v>LIKENASTIA</v>
       </c>
@@ -2331,7 +2399,7 @@
       <c r="D16" s="6">
         <v>163</v>
       </c>
-      <c r="E16" s="19" t="str">
+      <c r="E16" s="18" t="str">
         <f t="shared" si="0"/>
         <v>COCOMELON - NURSERY RHYMES</v>
       </c>
@@ -2358,7 +2426,7 @@
       <c r="D17" s="6">
         <v>66</v>
       </c>
-      <c r="E17" s="19" t="str">
+      <c r="E17" s="18" t="str">
         <f t="shared" si="0"/>
         <v>CANAL KONDZILLA</v>
       </c>
@@ -2385,7 +2453,7 @@
       <c r="D18" s="6">
         <v>115</v>
       </c>
-      <c r="E18" s="19" t="str">
+      <c r="E18" s="18" t="str">
         <f t="shared" si="0"/>
         <v>KIDS D IANA SHOW</v>
       </c>
@@ -2412,7 +2480,7 @@
       <c r="D19" s="6">
         <v>44</v>
       </c>
-      <c r="E19" s="19" t="str">
+      <c r="E19" s="18" t="str">
         <f t="shared" si="0"/>
         <v>BADABUN</v>
       </c>
@@ -2439,7 +2507,7 @@
       <c r="D20" s="6">
         <v>25</v>
       </c>
-      <c r="E20" s="19" t="str">
+      <c r="E20" s="18" t="str">
         <f t="shared" si="0"/>
         <v>VANOSSGAMING</v>
       </c>
@@ -2466,7 +2534,7 @@
       <c r="D21" s="6">
         <v>35</v>
       </c>
-      <c r="E21" s="19" t="str">
+      <c r="E21" s="18" t="str">
         <f t="shared" si="0"/>
         <v>MARKIPLIER</v>
       </c>
@@ -2481,7 +2549,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E22" s="20"/>
+      <c r="E22" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2494,30 +2562,30 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" style="25" customWidth="1"/>
-    <col min="3" max="3" width="17.08984375" style="25" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" style="25" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="25" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" style="24" customWidth="1"/>
+    <col min="3" max="3" width="17.08984375" style="24" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="24" customWidth="1"/>
     <col min="7" max="7" width="15.08984375" customWidth="1"/>
     <col min="8" max="8" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="26" t="s">
+      <c r="D1" s="21"/>
+      <c r="E1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="27"/>
+      <c r="F1" s="26"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -2532,10 +2600,10 @@
       <c r="C2" s="6">
         <v>10000000</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="27" t="str">
+      <c r="F2" s="26" t="str">
         <f>LEFT(A2,5)</f>
         <v>Pavan</v>
       </c>
@@ -2562,22 +2630,22 @@
       <c r="C3" s="6">
         <v>100000000</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="27" t="str">
+      <c r="F3" s="26" t="str">
         <f>RIGHT(A2,5)</f>
         <v>Kumar</v>
       </c>
-      <c r="G3" s="27" t="str">
+      <c r="G3" s="26" t="str">
         <f>RIGHT(A3,4)</f>
         <v>Syed</v>
       </c>
-      <c r="H3" s="27" t="str">
+      <c r="H3" s="26" t="str">
         <f>RIGHT(A4,5)</f>
         <v>Kumar</v>
       </c>
-      <c r="I3" s="27" t="str">
+      <c r="I3" s="26" t="str">
         <f>RIGHT(A5,5)</f>
         <v>Chiru</v>
       </c>
@@ -2623,22 +2691,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2721,6 +2789,500 @@
         <v xml:space="preserve">Sai </v>
       </c>
       <c r="H5" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DD7116-14F7-483C-A063-432312259810}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="6">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="D2" s="6">
+        <f>LEN(A2)</f>
+        <v>11</v>
+      </c>
+      <c r="F2" s="6">
+        <f>FIND(" ",A2)</f>
+        <v>6</v>
+      </c>
+      <c r="G2" s="24">
+        <v>5</v>
+      </c>
+      <c r="H2" s="8" t="str">
+        <f>LEFT(A2,FIND(" ",A2)-1)</f>
+        <v>Pavan</v>
+      </c>
+      <c r="I2" s="8" t="str">
+        <f>RIGHT(A2,LEN(A2)-FIND(" ",A2))</f>
+        <v>Kumar</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="6">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:D5" si="0">LEN(A3)</f>
+        <v>16</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" ref="F3:F5" si="1">FIND(" ",A3)</f>
+        <v>12</v>
+      </c>
+      <c r="G3" s="24">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8" t="str">
+        <f t="shared" ref="H3:H5" si="2">LEFT(A3,FIND(" ",A3)-1)</f>
+        <v>Zameeruddin</v>
+      </c>
+      <c r="I3" s="8" t="str">
+        <f t="shared" ref="I3:I5" si="3">RIGHT(A3,LEN(A3)-FIND(" ",A3))</f>
+        <v>Syed</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="6">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="G4" s="24">
+        <v>5</v>
+      </c>
+      <c r="H4" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Shiva</v>
+      </c>
+      <c r="I4" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>Kumar</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="6">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="24">
+        <v>5</v>
+      </c>
+      <c r="H5" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Sai</v>
+      </c>
+      <c r="I5" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>Chiru</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F507B5-92F2-4D75-9012-8EC2AC07B4BD}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.90625" customWidth="1"/>
+    <col min="7" max="8" width="17.36328125" customWidth="1"/>
+    <col min="9" max="9" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2">
+        <v>1234567890</v>
+      </c>
+      <c r="F2" t="str">
+        <f>A2 &amp; " " &amp; B2</f>
+        <v>Pavan Kumar</v>
+      </c>
+      <c r="G2" t="str">
+        <f>_xlfn.CONCAT(A2," ",B2)</f>
+        <v>Pavan Kumar</v>
+      </c>
+      <c r="H2" t="str">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,A2:B2)</f>
+        <v>Pavan Kumar</v>
+      </c>
+      <c r="I2" t="str">
+        <f>_xlfn.CONCAT(A2," ", B2,"@",C2)</f>
+        <v>Pavan Kumar@1234567890</v>
+      </c>
+      <c r="J2" t="str">
+        <f>_xlfn.TEXTJOIN("@",TRUE,A2:C2)</f>
+        <v>Pavan@Kumar@1234567890</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>2536251425</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F5" si="0">A3 &amp; " " &amp; B3</f>
+        <v>Zameeruddin Syed</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G5" si="1">_xlfn.CONCAT(A3," ",B3)</f>
+        <v>Zameeruddin Syed</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H5" si="2">_xlfn.TEXTJOIN(" ",TRUE,A3:B3)</f>
+        <v>Zameeruddin Syed</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I5" si="3">_xlfn.CONCAT(A3," ", B3,"@",C3)</f>
+        <v>Zameeruddin Syed@2536251425</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J5" si="4">_xlfn.TEXTJOIN("@",TRUE,A3:C3)</f>
+        <v>Zameeruddin@Syed@2536251425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>9865986568</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>Shiva Kumar</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v>Shiva Kumar</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="2"/>
+        <v>Shiva Kumar</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="3"/>
+        <v>Shiva Kumar@9865986568</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="4"/>
+        <v>Shiva@Kumar@9865986568</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>2556851425</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>Sai Chiru</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>Sai Chiru</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="2"/>
+        <v>Sai Chiru</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="3"/>
+        <v>Sai Chiru@2556851425</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="4"/>
+        <v>Sai@Chiru@2556851425</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81EF5D6-2748-4FC1-82ED-B266986A79F6}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="27.08984375" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="31.1796875" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="24">
+        <v>1234567890</v>
+      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="32" t="str">
+        <f>_xlfn.CONCAT(A2:B2,"@anudip.org")</f>
+        <v>PavanKumar@anudip.org</v>
+      </c>
+      <c r="G2" s="32" t="str">
+        <f>_xlfn.CONCAT(A2,B2,RIGHT(C2,4),"@anudip.org")</f>
+        <v>PavanKumar7890@anudip.org</v>
+      </c>
+      <c r="H2" s="32" t="str">
+        <f>_xlfn.CONCAT(A2,B2,LEFT(C2,4),"@anudip.org")</f>
+        <v>PavanKumar1234@anudip.org</v>
+      </c>
+      <c r="I2" t="str">
+        <f>_xlfn.CONCAT(A2,B2,MID(C2,4,4),"@anudip.org")</f>
+        <v>PavanKumar4567@anudip.org</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="24">
+        <v>2536251425</v>
+      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="32" t="str">
+        <f t="shared" ref="F3:F5" si="0">_xlfn.CONCAT(A3:B3,"@anudip.org")</f>
+        <v>ZameeruddinSyed@anudip.org</v>
+      </c>
+      <c r="G3" s="32" t="str">
+        <f t="shared" ref="G3:G5" si="1">_xlfn.CONCAT(A3,B3,RIGHT(C3,4),"@anudip.org")</f>
+        <v>ZameeruddinSyed1425@anudip.org</v>
+      </c>
+      <c r="H3" s="32" t="str">
+        <f t="shared" ref="H3:H6" si="2">_xlfn.CONCAT(A3,B3,LEFT(C3,4),"@anudip.org")</f>
+        <v>ZameeruddinSyed2536@anudip.org</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I5" si="3">_xlfn.CONCAT(A3,B3,MID(C3,4,4),"@anudip.org")</f>
+        <v>ZameeruddinSyed6251@anudip.org</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="24">
+        <v>9865986568</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>ShivaKumar@anudip.org</v>
+      </c>
+      <c r="G4" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>ShivaKumar6568@anudip.org</v>
+      </c>
+      <c r="H4" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>ShivaKumar9865@anudip.org</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="3"/>
+        <v>ShivaKumar5986@anudip.org</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="24">
+        <v>2556851425</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>SaiChiru@anudip.org</v>
+      </c>
+      <c r="G5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>SaiChiru1425@anudip.org</v>
+      </c>
+      <c r="H5" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>SaiChiru2556@anudip.org</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="3"/>
+        <v>SaiChiru6851@anudip.org</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
